--- a/examples/HO_SO_CAU_KM19_529/00_BAN_CHI_HUY_MASTER/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/00_BAN_CHI_HUY_MASTER/Ho_So_KCS_QS_TienDo_Cau_Km19+529.080.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baotu\Downloads\HSTK Cầu Km19+529.080_Marker\01_HIEN_TRUONG_QLCL_KCS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_A7A2110BF42D65B7F9B298DA41CDAFD34E8B02FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
